--- a/coronavirus_response_forms/001_negative_covid_19_test_reporting_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/001_negative_covid_19_test_reporting_form--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1259,29 +1259,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shortness of Breath</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>result_symptom_1_choices</t>
+          <t>result_symptom_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fever</t>
+          <t>Sore Throat</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>runny_nose/headache</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>Runny Nose/Headache</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>runny_nose/headache</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Runny Nose/Headache</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1361,46 +1361,46 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>result_symptom_2_choices</t>
+          <t>result_symptom_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shortness of Breath</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>result_symptom_2_choices</t>
+          <t>result_symptom_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Sore Throat</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fever</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>runny_nose/headache</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Runny Nose/Headache</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1463,63 +1463,63 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>runny_nose/headache</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Runny Nose/Headache</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>result_symptom_3_choices</t>
+          <t>result_symptom_4_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>result_symptom_3_choices</t>
+          <t>result_symptom_4_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shortness of Breath</t>
+          <t>Sore Throat</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>result_symptom_3_choices</t>
+          <t>result_symptom_4_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>runny_nose/headache</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fever</t>
+          <t>Runny Nose/Headache</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1565,36 +1565,36 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>result_symptom_4_choices</t>
+          <t>result_symptom_5_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>runny_nose/headache</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Runny Nose/Headache</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>result_symptom_4_choices</t>
+          <t>result_symptom_5_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1611,34 +1611,34 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>result_symptom_4_choices</t>
+          <t>result_symptom_5_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Shortness of Breath</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>result_symptom_4_choices</t>
+          <t>result_symptom_5_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>runny_nose/headache</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Runny Nose/Headache</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fever</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1667,97 +1667,97 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>result_symptom_5_choices</t>
+          <t>result_symptom_6_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cough</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>result_symptom_5_choices</t>
+          <t>result_symptom_6_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>runny_nose/headache</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Runny Nose/Headache</t>
+          <t>Sore Throat</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>result_symptom_5_choices</t>
+          <t>result_symptom_6_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sore Throat</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>result_symptom_5_choices</t>
+          <t>result_symptom_6_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>runny_nose/headache</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shortness of Breath</t>
+          <t>Runny Nose/Headache</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>result_symptom_5_choices</t>
+          <t>result_symptom_6_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -1769,112 +1769,10 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
-        <is>
-          <t>Fever</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>result_symptom_6_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>sore_throat</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Sore Throat</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>result_symptom_6_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>cough</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Cough</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>result_symptom_6_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>runny_nose/headache</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Runny Nose/Headache</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>result_symptom_6_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>sore_throat</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Sore Throat</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>result_symptom_6_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shortness_of_breath</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Shortness of Breath</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>result_symptom_6_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>fatigue</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
         <is>
           <t>Fatigue</t>
         </is>
